--- a/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
@@ -69,18 +69,6 @@
     <x:t>E</x:t>
   </x:si>
   <x:si>
-    <x:t>BB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EE</x:t>
-  </x:si>
-  <x:si>
     <x:t>2D 1x1</x:t>
   </x:si>
   <x:si>
@@ -88,27 +76,6 @@
   </x:si>
   <x:si>
     <x:t>Input2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D3</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -598,17 +565,17 @@
         <x:f t="dataTable" ref="C4:G4" dtr="1" r1="A1" ca="1"/>
         <x:v>AA</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>11</x:v>
+      <x:c r="D4" s="0" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="str">
+        <x:v>CC</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="str">
+        <x:v>DD</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="str">
+        <x:v>EE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -630,7 +597,7 @@
   <x:sheetData>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -653,7 +620,7 @@
     </x:row>
     <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>3</x:v>
@@ -661,7 +628,7 @@
     </x:row>
     <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>1</x:v>
@@ -686,7 +653,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="A1" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
         <x:v>1</x:v>
@@ -694,7 +661,7 @@
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>1</x:v>
@@ -720,41 +687,41 @@
         <x:f t="dataTable" ref="C5:D8" dt2D="1" r1="B2" r2="B1" ca="1"/>
         <x:v>A2</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="D5" s="0" t="str">
+        <x:v>A3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="C6" s="0" t="str">
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="str">
+        <x:v>B3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B7" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>19</x:v>
+      <x:c r="C7" s="0" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="str">
+        <x:v>C3</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B8" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>21</x:v>
+      <x:c r="C8" s="0" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="str">
+        <x:v>D3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
